--- a/DataTables/FACTURACION/EmitirAnticipoSacsa.xlsx
+++ b/DataTables/FACTURACION/EmitirAnticipoSacsa.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="903" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="903" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="1" state="visible" r:id="rId1"/>
@@ -20,7 +20,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'general'!$B$1:$Q$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'conceptoAnticipos'!$A$1:$H$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'conceptoAnticipos'!$B$1:$I$1</definedName>
   </definedNames>
   <calcPr calcId="181029" fullCalcOnLoad="1"/>
 </workbook>
@@ -1038,12 +1038,12 @@
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>14/04/2025</t>
+          <t>25/03/2026</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr">
         <is>
-          <t>0003-00001451</t>
+          <t>0003-00001694</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -1063,7 +1063,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>ABRIL</t>
+          <t>MARZO</t>
         </is>
       </c>
       <c r="I2" s="17" t="inlineStr">
@@ -1078,7 +1078,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2025-VEN-286</t>
+          <t>2026-VEN-268</t>
         </is>
       </c>
       <c r="L2" s="23" t="inlineStr"/>
@@ -1101,12 +1101,12 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>14/04/2025</t>
+          <t>25/03/2026</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr">
         <is>
-          <t>0003-00001452</t>
+          <t>0003-00001695</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>ABRIL</t>
+          <t>MARZO</t>
         </is>
       </c>
       <c r="I3" s="17" t="inlineStr">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2025-VEN-287</t>
+          <t>2026-VEN-269</t>
         </is>
       </c>
       <c r="L3" s="23" t="inlineStr"/>
@@ -1164,12 +1164,12 @@
       </c>
       <c r="C4" s="1" t="inlineStr">
         <is>
-          <t>14/04/2025</t>
+          <t>25/03/2026</t>
         </is>
       </c>
       <c r="D4" s="1" t="inlineStr">
         <is>
-          <t>0003-00001453</t>
+          <t>0003-00001696</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1189,7 +1189,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>ABRIL</t>
+          <t>MARZO</t>
         </is>
       </c>
       <c r="I4" s="17" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2025-VEN-288</t>
+          <t>2026-VEN-270</t>
         </is>
       </c>
       <c r="L4" s="23" t="inlineStr"/>
@@ -1227,12 +1227,12 @@
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>14/04/2025</t>
+          <t>25/03/2026</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr">
         <is>
-          <t>0003-00001454</t>
+          <t>0003-00001697</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>ABRIL</t>
+          <t>MARZO</t>
         </is>
       </c>
       <c r="I5" s="17" t="inlineStr">
@@ -1267,7 +1267,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2025-VEN-289</t>
+          <t>2026-VEN-271</t>
         </is>
       </c>
       <c r="L5" s="23" t="inlineStr"/>
@@ -1290,12 +1290,12 @@
       </c>
       <c r="C6" s="1" t="inlineStr">
         <is>
-          <t>14/04/2025</t>
+          <t>25/03/2026</t>
         </is>
       </c>
       <c r="D6" s="1" t="inlineStr">
         <is>
-          <t>0003-00001455</t>
+          <t>0003-00001698</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1315,22 +1315,22 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>ABRIL</t>
+          <t>MARZO</t>
         </is>
       </c>
       <c r="I6" s="17" t="inlineStr">
         <is>
-          <t>1210000</t>
+          <t>1936000</t>
         </is>
       </c>
       <c r="J6" s="22" t="inlineStr">
         <is>
-          <t>1210000</t>
+          <t>1936000</t>
         </is>
       </c>
       <c r="K6" s="1" t="inlineStr">
         <is>
-          <t>2025-VEN-290</t>
+          <t>2026-VEN-272</t>
         </is>
       </c>
       <c r="L6" s="23" t="inlineStr"/>
@@ -1353,12 +1353,12 @@
       </c>
       <c r="C7" s="1" t="inlineStr">
         <is>
-          <t>14/04/2025</t>
+          <t>25/03/2026</t>
         </is>
       </c>
       <c r="D7" s="1" t="inlineStr">
         <is>
-          <t>0003-00001456</t>
+          <t>0003-00001699</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>ABRIL</t>
+          <t>MARZO</t>
         </is>
       </c>
       <c r="I7" s="17" t="inlineStr">
@@ -1393,7 +1393,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2025-VEN-291</t>
+          <t>2026-VEN-273</t>
         </is>
       </c>
       <c r="L7" s="23" t="inlineStr"/>
@@ -1406,7 +1406,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1416,14 +1416,10 @@
       </c>
       <c r="C8" s="1" t="inlineStr">
         <is>
-          <t>14/04/2025</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="inlineStr">
-        <is>
-          <t>0003-00001457</t>
-        </is>
-      </c>
+          <t>25/03/2026</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>LOS NATIVOS S.A.</t>
@@ -1441,7 +1437,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>ABRIL</t>
+          <t>MARZO</t>
         </is>
       </c>
       <c r="I8" s="17" t="inlineStr">
@@ -1449,16 +1445,8 @@
           <t>726000</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>726000</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>2025-VEN-292</t>
-        </is>
-      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
       <c r="L8" s="23" t="inlineStr"/>
       <c r="M8" s="24" t="inlineStr"/>
       <c r="N8" s="24" t="inlineStr"/>
@@ -1479,12 +1467,12 @@
       </c>
       <c r="C9" s="1" t="inlineStr">
         <is>
-          <t>14/04/2025</t>
+          <t>25/03/2026</t>
         </is>
       </c>
       <c r="D9" s="1" t="inlineStr">
         <is>
-          <t>0003-00001458</t>
+          <t>0003-00001700</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1504,7 +1492,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>ABRIL</t>
+          <t>MARZO</t>
         </is>
       </c>
       <c r="I9" s="17" t="inlineStr">
@@ -1519,7 +1507,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2025-VEN-293</t>
+          <t>2026-VEN-274</t>
         </is>
       </c>
       <c r="L9" s="23" t="inlineStr"/>
@@ -2307,60 +2295,65 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:J21"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15"/>
   <cols>
-    <col width="33.5703125" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="21.85546875" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="9.7109375" bestFit="1" customWidth="1" min="3" max="3"/>
-    <col width="14" bestFit="1" customWidth="1" style="10" min="4" max="4"/>
-    <col width="28.42578125" bestFit="1" customWidth="1" min="5" max="5"/>
-    <col width="16.7109375" bestFit="1" customWidth="1" min="8" max="8"/>
-    <col width="17" bestFit="1" customWidth="1" min="9" max="9"/>
+    <col width="33.5703125" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="21.85546875" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="9.7109375" bestFit="1" customWidth="1" min="4" max="4"/>
+    <col width="14" bestFit="1" customWidth="1" style="10" min="5" max="5"/>
+    <col width="28.42578125" bestFit="1" customWidth="1" min="6" max="6"/>
+    <col width="16.7109375" bestFit="1" customWidth="1" min="9" max="9"/>
+    <col width="17" bestFit="1" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>i_anticipo</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>t_cliente</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>i_centroCosto</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="D1" s="4" t="inlineStr">
         <is>
           <t>i_alicuota</t>
         </is>
       </c>
-      <c r="D1" s="9" t="inlineStr">
+      <c r="E1" s="9" t="inlineStr">
         <is>
           <t>i_netoGravado</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>i_descripcion</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>i_tipoItem</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>i_unidades</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>i_cuentaContable</t>
         </is>
       </c>
-      <c r="I1" s="24" t="inlineStr">
+      <c r="J1" s="24" t="inlineStr">
         <is>
           <t>formatoNumero</t>
         </is>
@@ -2369,362 +2362,402 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
           <t>FINCA LAS MAGDALENAS S. A. S.</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>EST-ESTRUCTURA</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>IVA (21%)</t>
         </is>
       </c>
-      <c r="D2" s="10" t="inlineStr">
+      <c r="E2" s="10" t="inlineStr">
         <is>
           <t>450000</t>
         </is>
       </c>
-      <c r="E2" s="5" t="inlineStr">
+      <c r="F2" s="5" t="inlineStr">
         <is>
           <t>ANTICIPO</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>Concepto</t>
         </is>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>1</v>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>570101009</t>
         </is>
       </c>
-      <c r="I2" s="24">
-        <f>VALUE(D2)</f>
+      <c r="J2" s="24">
+        <f>VALUE(E2)</f>
         <v/>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
           <t>FINCAS Y BODEGAS MONTECHEZ S.A.</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>EST-ESTRUCTURA</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>IVA (21%)</t>
         </is>
       </c>
-      <c r="D3" s="10" t="inlineStr">
+      <c r="E3" s="10" t="inlineStr">
         <is>
           <t>150000</t>
         </is>
       </c>
-      <c r="E3" s="5" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>ANTICIPO</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>Concepto</t>
         </is>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
         <v>1</v>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>570101009</t>
         </is>
       </c>
-      <c r="I3" s="24">
-        <f>VALUE(D3)</f>
+      <c r="J3" s="24">
+        <f>VALUE(E3)</f>
         <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
           <t>FOA AGUAS DE ALTAMIRA</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>EST-ESTRUCTURA</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>IVA (21%)</t>
         </is>
       </c>
-      <c r="D4" s="10" t="inlineStr">
+      <c r="E4" s="10" t="inlineStr">
         <is>
           <t>90000</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>ANTICIPO</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>Concepto</t>
         </is>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>1</v>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>570101009</t>
         </is>
       </c>
-      <c r="I4" s="24">
-        <f>VALUE(D4)</f>
+      <c r="J4" s="24">
+        <f>VALUE(E4)</f>
         <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
           <t>FOI TERRUÑOS DE LOS ANDES</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>EST-ESTRUCTURA</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>IVA (21%)</t>
         </is>
       </c>
-      <c r="D5" s="10" t="inlineStr">
+      <c r="E5" s="10" t="inlineStr">
         <is>
           <t>1500000</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>ANTICIPO</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>Concepto</t>
         </is>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
         <v>1</v>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>570101009</t>
         </is>
       </c>
-      <c r="I5" s="24">
-        <f>VALUE(D5)</f>
+      <c r="J5" s="24">
+        <f>VALUE(E5)</f>
         <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
           <t>GRANAR S.A.C y F.</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>EST-ESTRUCTURA</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>IVA (21%)</t>
         </is>
       </c>
-      <c r="D6" s="10" t="inlineStr">
+      <c r="E6" s="10" t="inlineStr">
         <is>
           <t>1000000</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>ANTICIPO</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>Concepto</t>
         </is>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
         <v>1</v>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>570101009</t>
         </is>
       </c>
-      <c r="I6" s="24">
-        <f>VALUE(D6)</f>
+      <c r="J6" s="24">
+        <f>VALUE(E6)</f>
         <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
           <t>LLORENTE HNOS SA</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>EST-ESTRUCTURA</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>IVA (21%)</t>
         </is>
       </c>
-      <c r="D7" s="10" t="inlineStr">
+      <c r="E7" s="10" t="inlineStr">
         <is>
           <t>450000</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>ANTICIPO</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>Concepto</t>
         </is>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
         <v>1</v>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>570101009</t>
         </is>
       </c>
-      <c r="I7" s="24">
-        <f>VALUE(D7)</f>
+      <c r="J7" s="24">
+        <f>VALUE(E7)</f>
         <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>LOS NATIVOS S.A.</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
+          <t>GRANAR S.A.C y F.</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
           <t>EST-ESTRUCTURA</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>IVA (21%)</t>
         </is>
       </c>
-      <c r="D8" s="10" t="inlineStr">
+      <c r="E8" s="10" t="inlineStr">
         <is>
           <t>600000</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>ANTICIPO</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>ANTICIPO (LN)</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
         <is>
           <t>Concepto</t>
         </is>
       </c>
-      <c r="G8" t="n">
+      <c r="H8" t="n">
         <v>1</v>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>570101009</t>
         </is>
       </c>
-      <c r="I8" s="24">
-        <f>VALUE(D8)</f>
+      <c r="J8" s="24">
+        <f>VALUE(E8)</f>
         <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
           <t>TELLERIA JUAN GABRIEL</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>EST-ESTRUCTURA</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>IVA (21%)</t>
         </is>
       </c>
-      <c r="D9" s="10" t="inlineStr">
+      <c r="E9" s="10" t="inlineStr">
         <is>
           <t>450000</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="F9" s="5" t="inlineStr">
         <is>
           <t>ANTICIPO</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>Concepto</t>
         </is>
       </c>
-      <c r="G9" t="n">
+      <c r="H9" t="n">
         <v>1</v>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="I9" s="2" t="inlineStr">
         <is>
           <t>570101009</t>
         </is>
       </c>
-      <c r="I9" s="24">
-        <f>VALUE(D9)</f>
+      <c r="J9" s="24">
+        <f>VALUE(E9)</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="E21" s="3" t="n"/>
+      <c r="F21" s="3" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H1">
-    <sortState ref="A2:H9">
-      <sortCondition ref="A1"/>
+  <autoFilter ref="B1:I1">
+    <sortState ref="B2:I9">
+      <sortCondition ref="B1"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
